--- a/template2-and-clean-gh-pages/ig/ValueSet-act-type-ror-valueset.xlsx
+++ b/template2-and-clean-gh-pages/ig/ValueSet-act-type-ror-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T08:16:41+00:00</t>
+    <t>2026-07-24T08:25:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
